--- a/artfynd/A 32441-2026 artfynd.xlsx
+++ b/artfynd/A 32441-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136141633</v>
       </c>
       <c r="B2" t="n">
-        <v>80560</v>
+        <v>80561</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136141624</v>
       </c>
       <c r="B3" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136141625</v>
       </c>
       <c r="B4" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>136141628</v>
       </c>
       <c r="B5" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
         <v>136141632</v>
       </c>
       <c r="B6" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>136141622</v>
       </c>
       <c r="B7" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>136141769</v>
       </c>
       <c r="B8" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 32441-2026 artfynd.xlsx
+++ b/artfynd/A 32441-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136141633</v>
       </c>
       <c r="B2" t="n">
-        <v>80561</v>
+        <v>80565</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136141624</v>
       </c>
       <c r="B3" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136141625</v>
       </c>
       <c r="B4" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>136141628</v>
       </c>
       <c r="B5" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
         <v>136141632</v>
       </c>
       <c r="B6" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>136141622</v>
       </c>
       <c r="B7" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>136141769</v>
       </c>
       <c r="B8" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 32441-2026 artfynd.xlsx
+++ b/artfynd/A 32441-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136141633</v>
       </c>
       <c r="B2" t="n">
-        <v>80565</v>
+        <v>80566</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136141624</v>
       </c>
       <c r="B3" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136141625</v>
       </c>
       <c r="B4" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>136141628</v>
       </c>
       <c r="B5" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
         <v>136141632</v>
       </c>
       <c r="B6" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>136141622</v>
       </c>
       <c r="B7" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>136141769</v>
       </c>
       <c r="B8" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 32441-2026 artfynd.xlsx
+++ b/artfynd/A 32441-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136141633</v>
       </c>
       <c r="B2" t="n">
-        <v>80566</v>
+        <v>80570</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136141624</v>
       </c>
       <c r="B3" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136141625</v>
       </c>
       <c r="B4" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>136141628</v>
       </c>
       <c r="B5" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
         <v>136141632</v>
       </c>
       <c r="B6" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 32441-2026 artfynd.xlsx
+++ b/artfynd/A 32441-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136141633</v>
       </c>
       <c r="B2" t="n">
-        <v>80570</v>
+        <v>80576</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136141624</v>
       </c>
       <c r="B3" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136141625</v>
       </c>
       <c r="B4" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>136141628</v>
       </c>
       <c r="B5" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
         <v>136141632</v>
       </c>
       <c r="B6" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>136141622</v>
       </c>
       <c r="B7" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>136141769</v>
       </c>
       <c r="B8" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 32441-2026 artfynd.xlsx
+++ b/artfynd/A 32441-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136141633</v>
       </c>
       <c r="B2" t="n">
-        <v>80576</v>
+        <v>80589</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136141624</v>
       </c>
       <c r="B3" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136141625</v>
       </c>
       <c r="B4" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>136141628</v>
       </c>
       <c r="B5" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
         <v>136141632</v>
       </c>
       <c r="B6" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>136141622</v>
       </c>
       <c r="B7" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>136141769</v>
       </c>
       <c r="B8" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 32441-2026 artfynd.xlsx
+++ b/artfynd/A 32441-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136141633</v>
       </c>
       <c r="B2" t="n">
-        <v>80589</v>
+        <v>80590</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136141624</v>
       </c>
       <c r="B3" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136141625</v>
       </c>
       <c r="B4" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>136141628</v>
       </c>
       <c r="B5" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
         <v>136141632</v>
       </c>
       <c r="B6" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
